--- a/master/result/79_霸道总裁：独家宠爱/79_职场女王_霸道总裁.xlsx
+++ b/master/result/79_霸道总裁：独家宠爱/79_职场女王_霸道总裁.xlsx
@@ -397,588 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>nowadays</v>
       </c>
       <c r="B2" t="str">
-        <v>nowadays</v>
+        <v>/nowadays/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>现今</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>duty</v>
       </c>
       <c r="B3" t="str">
-        <v>duty</v>
+        <v>/duty/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>责任</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>crucial</v>
       </c>
       <c r="B4" t="str">
-        <v>crucial</v>
+        <v>/crucial/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>至关重要的</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>assignment</v>
       </c>
       <c r="B5" t="str">
-        <v>assignment</v>
+        <v>/əˈsaɪnmənt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>任务</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>specify</v>
       </c>
       <c r="B6" t="str">
-        <v>specify</v>
+        <v>/specify/</v>
       </c>
       <c r="C6" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>详细说明</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>ambassador</v>
       </c>
       <c r="B7" t="str">
-        <v>ambassador</v>
+        <v>/ambassador/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>大使</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>pork</v>
       </c>
       <c r="B8" t="str">
-        <v>pork</v>
+        <v>/pork/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>猪肉</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>wealthy</v>
       </c>
       <c r="B9" t="str">
-        <v>wealthy</v>
+        <v>/wealthy/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>富有的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>praise</v>
       </c>
       <c r="B10" t="str">
-        <v>praise</v>
+        <v>/praise/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>称赞</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>highly</v>
       </c>
       <c r="B11" t="str">
-        <v>highly</v>
+        <v>/highly/</v>
       </c>
       <c r="C11" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>高度</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>park</v>
       </c>
       <c r="B12" t="str">
-        <v>park</v>
+        <v>/pɑːk/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>公园</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>golf</v>
       </c>
       <c r="B13" t="str">
-        <v>golf</v>
+        <v>/golf/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>高尔夫</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>ache</v>
       </c>
       <c r="B14" t="str">
-        <v>ache</v>
+        <v>/ache/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>疼痛</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>adult</v>
       </c>
       <c r="B15" t="str">
-        <v>adult</v>
+        <v>/adult/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>成年人</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>rebel</v>
       </c>
       <c r="B16" t="str">
-        <v>rebel</v>
+        <v>/rebel/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>叛逆者</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>movie</v>
       </c>
       <c r="B17" t="str">
-        <v>movie</v>
+        <v>/movie/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>电影</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>bald</v>
       </c>
       <c r="B18" t="str">
-        <v>bald</v>
+        <v>/bald/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>秃头</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>same</v>
       </c>
       <c r="B19" t="str">
-        <v>same</v>
+        <v>/same/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>同样</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>commence</v>
       </c>
       <c r="B20" t="str">
-        <v>commence</v>
+        <v>/commence/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>开始</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>each</v>
       </c>
       <c r="B21" t="str">
-        <v>each</v>
+        <v>/each/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>每</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>vest</v>
       </c>
       <c r="B22" t="str">
-        <v>vest</v>
+        <v>/vest/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>背心</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>sob</v>
       </c>
       <c r="B23" t="str">
-        <v>sob</v>
+        <v>/sob/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>哭泣</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>hurt</v>
       </c>
       <c r="B24" t="str">
-        <v>hurt</v>
+        <v>/hɜːt/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>伤心</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>relationship</v>
       </c>
       <c r="B25" t="str">
-        <v>relationship</v>
+        <v>/relationship/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>关系</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>mark</v>
       </c>
       <c r="B26" t="str">
-        <v>mark</v>
+        <v>/mɑːk/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>特色</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>arrest</v>
       </c>
       <c r="B27" t="str">
-        <v>arrest</v>
+        <v>/arrest/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>逮捕</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>ruthless</v>
       </c>
       <c r="B28" t="str">
-        <v>ruthless</v>
+        <v>/ruthless/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>果断</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>sex</v>
       </c>
       <c r="B29" t="str">
-        <v>sex</v>
+        <v>/sex/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>性别</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>evolution</v>
       </c>
       <c r="B30" t="str">
-        <v>evolution</v>
+        <v>/evolution/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>发展</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>heir</v>
       </c>
       <c r="B31" t="str">
-        <v>heir</v>
+        <v>/heir/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>继承人</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>Catholic</v>
       </c>
       <c r="B32" t="str">
-        <v>Catholic</v>
+        <v>/Catholic/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>天主教</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>carbon</v>
       </c>
       <c r="B33" t="str">
-        <v>carbon</v>
+        <v>/ˈkɑːbən/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>碳</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>last</v>
       </c>
       <c r="B34" t="str">
-        <v>last</v>
+        <v>/lɑːst/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>最后</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>agitate</v>
       </c>
       <c r="B35" t="str">
-        <v>agitate</v>
+        <v>/agitate/</v>
       </c>
       <c r="C35" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D35" t="str">
         <v>焦虑</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>quarrel</v>
       </c>
       <c r="B36" t="str">
-        <v>quarrel</v>
+        <v>/quarrel/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>争吵</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>imaginary</v>
       </c>
       <c r="B37" t="str">
-        <v>imaginary</v>
+        <v>/imaginary/</v>
       </c>
       <c r="C37" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>虚构的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>cricket</v>
       </c>
       <c r="B38" t="str">
+        <v>/cricket/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>蟋蟀</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>spelling</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/spelling/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>拼写</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>gulf</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/gulf/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>海湾</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>except</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/except/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>除...之外</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>blush</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/blush/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>脸红</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>transplant</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/transplant/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>移植</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>stretch</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/stretʃ/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>延伸</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>carrier</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/carrier/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>搬运工</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>zigzag</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/zigzag/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>曲折</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>quench</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/quench/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>抑制</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>roll</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/rəʊl/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>滚动</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
         <v>cricket</v>
       </c>
-      <c r="C38" t="str">
-        <v>蟋蟀</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>spelling</v>
-      </c>
-      <c r="C39" t="str">
-        <v>拼写</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>gulf</v>
-      </c>
-      <c r="C40" t="str">
-        <v>海湾</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>except</v>
-      </c>
-      <c r="C41" t="str">
-        <v>除...之外</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>blush</v>
-      </c>
-      <c r="C42" t="str">
-        <v>脸红</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>transplant</v>
-      </c>
-      <c r="C43" t="str">
-        <v>移植</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>stretch</v>
-      </c>
-      <c r="C44" t="str">
-        <v>延伸</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>carrier</v>
-      </c>
-      <c r="C45" t="str">
-        <v>搬运工</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>zigzag</v>
-      </c>
-      <c r="C46" t="str">
-        <v>曲折</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>quench</v>
-      </c>
-      <c r="C47" t="str">
-        <v>抑制</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>roll</v>
-      </c>
-      <c r="C48" t="str">
-        <v>滚动</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
       <c r="B49" t="str">
-        <v>cricket</v>
+        <v>/cricket/</v>
       </c>
       <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>板球</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>lap</v>
       </c>
       <c r="B50" t="str">
-        <v>lap</v>
+        <v>/lap/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>一圈</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>revolt</v>
       </c>
       <c r="B51" t="str">
-        <v>revolt</v>
+        <v>/revolt/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>反抗</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>shrink</v>
       </c>
       <c r="B52" t="str">
-        <v>shrink</v>
+        <v>/ʃrɪŋk/</v>
       </c>
       <c r="C52" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D52" t="str">
         <v>收缩</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>